--- a/MAJSushiConfig/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-service-request-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-service-request-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -465,7 +465,7 @@
     <t>method</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-method-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-method-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -485,7 +485,7 @@
     <t>author</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -586,7 +586,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -638,7 +638,7 @@
     <t>ServiceRequest.extension:author.extension:actor.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|Device|4.0.1|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-device-auteur-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-organization-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-related-person-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|Device|4.0.1|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-device-auteur-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-organization-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-related-person-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0)
 </t>
   </si>
   <si>
@@ -648,7 +648,7 @@
     <t>ServiceRequest.extension.url</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension</t>
   </si>
   <si>
     <t>ServiceRequest.extension:author.value[x]</t>
@@ -747,7 +747,7 @@
     <t>accessionNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-accession-number-identifier-document|0.1.0}
+    <t xml:space="preserve">Identifier {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-accession-number-identifier-document|0.1.0}
 </t>
   </si>
   <si>
@@ -1944,7 +1944,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="160.17578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="78.171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="74.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
